--- a/MATH/M01/bus123-math-m01-l01-starter.xlsx
+++ b/MATH/M01/bus123-math-m01-l01-starter.xlsx
@@ -2,26 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="580" windowWidth="25600" windowHeight="15240" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Next Class Challenge" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="10">
     <font>
       <name val="Calibri"/>
@@ -33,55 +30,55 @@
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="00355773"/>
+      <color rgb="FF355773"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Aptos"/>
-      <color rgb="001A1F2C"/>
+      <color rgb="FF1A1F2C"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="00B8843D"/>
+      <color rgb="FFB8843D"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Aptos"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="001A1F2C"/>
+      <color rgb="FF1A1F2C"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="00355773"/>
+      <color rgb="FF355773"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Aptos"/>
-      <color rgb="004A5567"/>
+      <color rgb="FF4A5567"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Aptos"/>
       <b val="1"/>
       <i val="1"/>
-      <color rgb="00355773"/>
+      <color rgb="FF355773"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -94,56 +91,56 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E1116"/>
+        <fgColor rgb="FF0E1116"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A7C5E"/>
+        <fgColor rgb="FF4A7C5E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAF3EC"/>
+        <fgColor rgb="FFEAF3EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAF8F3"/>
+        <fgColor rgb="FFFAF8F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00355773"/>
+        <fgColor rgb="FF355773"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD966"/>
+        <fgColor rgb="FFFFD966"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="009C4A2B"/>
+        <fgColor rgb="FF9C4A2B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00B8843D"/>
+        <fgColor rgb="FFB8843D"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -153,37 +150,63 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
       </left>
       <right style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
       </right>
       <top style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
       </top>
       <bottom style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color rgb="004A7C5E"/>
+        <color rgb="FF4A7C5E"/>
       </left>
       <right style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
       </right>
       <top style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
       </top>
       <bottom style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE5E1D6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFE5E1D6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE5E1D6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE5E1D6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFE5E1D6"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -191,35 +214,60 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
       </right>
       <top style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color rgb="FF4A7C5E"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFE5E1D6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF4A7C5E"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFE5E1D6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color rgb="00E5E1D6"/>
-      </top>
+      <top/>
       <bottom style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
       </right>
-      <top style="thin">
-        <color rgb="00E5E1D6"/>
-      </top>
+      <top/>
       <bottom style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -227,76 +275,95 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -304,49 +371,44 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00D9EAD3"/>
+          <fgColor rgb="FFF4CCCC"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00F4CCCC"/>
+          <fgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -713,189 +775,191 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" style="20" min="1" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="20">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>BUS 123 · MATH-M01-L01 · Whole Numbers, Fractions &amp; Percents</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="24" customHeight="1" s="20">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Meridian Advisory Group — Slide-to-Excel Starter Workbook</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="20">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>How This Workbook Fits the Lesson</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="6"/>
+    <row r="7" ht="24" customHeight="1" s="20">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>Open this workbook during the slide presentation.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="8" ht="24" customHeight="1" s="20">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>Use the Live You Try It tab when the deck pauses. The yellow cells are yours.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="9" ht="24" customHeight="1" s="20">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>Type formulas that start with = whenever possible. Use the visible input cells, not hardcoded answers.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="10" ht="24" customHeight="1" s="20">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>Feedback is gentle: Correct, Try again, or Check formula. The goal is practice, not grading.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="11" ht="24" customHeight="1" s="20">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>The Next Class Challenge is intentionally harder. We will use it to connect separate formulas into a small model.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>The Class Challenge is intentionally harder. Use it to connect separate formulas into a small model when class time allows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14" ht="24" customHeight="1" s="20">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>Tabs in This Workbook</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="15"/>
+    <row r="16" ht="28" customHeight="1" s="20">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Tab</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+    </row>
+    <row r="17" ht="34" customHeight="1" s="20">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>Live You Try It</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>Matches the slide deck micro-pauses exactly: whole numbers, fractions, and percents.</t>
         </is>
       </c>
-      <c r="C17" s="26" t="n"/>
-      <c r="D17" s="26" t="n"/>
-      <c r="E17" s="26" t="n"/>
-      <c r="F17" s="26" t="n"/>
-      <c r="G17" s="26" t="n"/>
-      <c r="H17" s="27" t="n"/>
-    </row>
-    <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Next Class Challenge</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="C17" s="23" t="n"/>
+      <c r="D17" s="23" t="n"/>
+      <c r="E17" s="23" t="n"/>
+      <c r="F17" s="23" t="n"/>
+      <c r="G17" s="23" t="n"/>
+      <c r="H17" s="24" t="n"/>
+    </row>
+    <row r="18" ht="34" customHeight="1" s="20">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>Class Challenge</t>
+        </is>
+      </c>
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>A richer next-class workshop that extends the same Meridian numbers into a multi-step model.</t>
         </is>
       </c>
-      <c r="C18" s="26" t="n"/>
-      <c r="D18" s="26" t="n"/>
-      <c r="E18" s="26" t="n"/>
-      <c r="F18" s="26" t="n"/>
-      <c r="G18" s="26" t="n"/>
-      <c r="H18" s="27" t="n"/>
-    </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="C18" s="23" t="n"/>
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="23" t="n"/>
+      <c r="F18" s="23" t="n"/>
+      <c r="G18" s="23" t="n"/>
+      <c r="H18" s="24" t="n"/>
+    </row>
+    <row r="19" ht="34" customHeight="1" s="20">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>FormulaReferenceCard</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>Quick syntax reminders for arithmetic, fractions, and percent formulas.</t>
         </is>
       </c>
-      <c r="C19" s="26" t="n"/>
-      <c r="D19" s="26" t="n"/>
-      <c r="E19" s="26" t="n"/>
-      <c r="F19" s="26" t="n"/>
-      <c r="G19" s="26" t="n"/>
-      <c r="H19" s="27" t="n"/>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="C19" s="23" t="n"/>
+      <c r="D19" s="23" t="n"/>
+      <c r="E19" s="23" t="n"/>
+      <c r="F19" s="23" t="n"/>
+      <c r="G19" s="23" t="n"/>
+      <c r="H19" s="24" t="n"/>
+    </row>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22" ht="24" customHeight="1" s="20">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>Before Class Ends</t>
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>Complete the Live You Try It tab. If you are moving quickly, preview the Next Class Challenge, but it is designed for the next class workshop.</t>
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>Complete the Live You Try It tab. If you are moving quickly, preview the Class Challenge; we can use it whenever class time allows.</t>
         </is>
       </c>
     </row>
@@ -905,8 +969,8 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B8:H8"/>
     <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B18:H18"/>
     <mergeCell ref="B9:H9"/>
-    <mergeCell ref="B18:H18"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="B7:H7"/>
@@ -918,7 +982,7 @@
     <mergeCell ref="A24:H25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="portrait" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -929,377 +993,395 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" style="20" min="1" max="1"/>
+    <col width="34" customWidth="1" style="20" min="2" max="2"/>
+    <col width="14" customWidth="1" style="20" min="3" max="4"/>
+    <col width="18" customWidth="1" style="20" min="5" max="6"/>
+    <col width="31" customWidth="1" style="20" min="7" max="7"/>
+    <col width="14" customWidth="1" style="20" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="20">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>Live You Try It · Match the Slide Numbers</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="29" t="inlineStr">
+    <row r="2" ht="16" customHeight="1" s="20">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>Type formulas in yellow cells while the deck pauses.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5" ht="32" customHeight="1" s="20">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Slide</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Input A</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Input B</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Your Formula / Answer</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Feedback</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Formula Hint</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Skill</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
+    <row r="6" ht="40" customHeight="1" s="20">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Whole Numbers 1: New account count</t>
         </is>
       </c>
-      <c r="C6" s="30" t="n">
+      <c r="C6" s="15" t="n">
         <v>57</v>
       </c>
-      <c r="D6" s="30" t="n">
+      <c r="D6" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="31" t="inlineStr"/>
-      <c r="F6" s="11">
+      <c r="E6" s="16" t="n"/>
+      <c r="F6" s="6">
         <f>IF(E6="","",IF(ABS(E6-(C6-D6))&lt;0.0001,"Correct","Try again"))</f>
         <v/>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>'=starting accounts - lost accounts</t>
         </is>
       </c>
-      <c r="H6" s="30" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>Subtract</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="32" t="inlineStr">
+    <row r="7" ht="40" customHeight="1" s="20">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B7" s="32" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Whole Numbers 2: New quarterly fee revenue</t>
         </is>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="17">
         <f>E6</f>
         <v/>
       </c>
-      <c r="D7" s="32" t="n">
+      <c r="D7" s="17" t="n">
         <v>4200</v>
       </c>
-      <c r="E7" s="31" t="inlineStr"/>
-      <c r="F7" s="11">
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="6">
         <f>IF(E7="","",IF(ABS(E7-(E6*D7))&lt;0.01,"Correct","Try again"))</f>
         <v/>
       </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>'=new accounts * fee per account</t>
         </is>
       </c>
-      <c r="H7" s="32" t="inlineStr">
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t>Multiply</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
+    <row r="8" ht="40" customHeight="1" s="20">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Whole Numbers 3: Is the new revenue lower than prior $239,400?</t>
         </is>
       </c>
-      <c r="C8" s="30" t="inlineStr"/>
-      <c r="D8" s="30" t="inlineStr"/>
-      <c r="E8" s="10" t="inlineStr"/>
-      <c r="F8" s="11">
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="6">
         <f>IF(E8="","",IF(OR(LOWER(E8)="yes",LOWER(E8)="y"),"Correct","Check formula"))</f>
         <v/>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>Answer yes/no after comparing to prior revenue</t>
         </is>
       </c>
-      <c r="H8" s="30" t="inlineStr">
+      <c r="H8" s="15" t="inlineStr">
         <is>
           <t>Interpret</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="10" customHeight="1"/>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
+    <row r="9" ht="10" customHeight="1" s="20"/>
+    <row r="10" ht="40" customHeight="1" s="20">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Fractions 1: Tax advisors as decimal</t>
         </is>
       </c>
-      <c r="C10" s="30" t="n">
+      <c r="C10" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="D10" s="30" t="n">
+      <c r="D10" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="E10" s="31" t="inlineStr"/>
-      <c r="F10" s="11">
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="6">
         <f>IF(E10="","",IF(ABS(E10-(C10/D10))&lt;0.0001,"Correct","Try again"))</f>
         <v/>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>'=part / whole</t>
         </is>
       </c>
-      <c r="H10" s="30" t="inlineStr">
+      <c r="H10" s="15" t="inlineStr">
         <is>
           <t>Fraction</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="32" t="inlineStr">
+    <row r="11" ht="40" customHeight="1" s="20">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B11" s="32" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Fractions 2: Same result formatted as percent</t>
         </is>
       </c>
-      <c r="C11" s="32" t="n">
+      <c r="C11" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="33" t="n">
+      <c r="D11" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="E11" s="18" t="inlineStr"/>
-      <c r="F11" s="11">
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="6">
         <f>IF(E11="","",IF(ABS(E11-(C11/D11))&lt;0.0001,"Correct","Try again"))</f>
         <v/>
       </c>
-      <c r="G11" s="13" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>'=part / whole, then format as %</t>
         </is>
       </c>
-      <c r="H11" s="32" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>Percent format</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="30" t="inlineStr">
+    <row r="12" ht="40" customHeight="1" s="20">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Fractions 3: Did the denominator change from 6 to 9?</t>
         </is>
       </c>
-      <c r="C12" s="30" t="inlineStr"/>
-      <c r="D12" s="30" t="inlineStr"/>
-      <c r="E12" s="10" t="inlineStr"/>
-      <c r="F12" s="11">
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="6">
         <f>IF(E12="","",IF(OR(LOWER(E12)="yes",LOWER(E12)="y"),"Correct","Check denominator"))</f>
         <v/>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>Answer yes/no</t>
         </is>
       </c>
-      <c r="H12" s="30" t="inlineStr">
+      <c r="H12" s="15" t="inlineStr">
         <is>
           <t>Interpret</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="10" customHeight="1"/>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="30" t="inlineStr">
+    <row r="13" ht="10" customHeight="1" s="20"/>
+    <row r="14" ht="40" customHeight="1" s="20">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>Percents 1: 12% growth target</t>
         </is>
       </c>
-      <c r="C14" s="30" t="n">
+      <c r="C14" s="15" t="n">
         <v>239400</v>
       </c>
-      <c r="D14" s="34" t="n">
+      <c r="D14" s="18" t="n">
         <v>0.12</v>
       </c>
-      <c r="E14" s="31" t="inlineStr"/>
-      <c r="F14" s="11">
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="6">
         <f>IF(E14="","",IF(ABS(E14-(C14*(1+D14)))&lt;0.01,"Correct","Try again"))</f>
         <v/>
       </c>
-      <c r="G14" s="12" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>'=base * (1 + rate)</t>
         </is>
       </c>
-      <c r="H14" s="30" t="inlineStr">
+      <c r="H14" s="15" t="inlineStr">
         <is>
           <t>Growth target</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="32" t="inlineStr">
+    <row r="15" ht="40" customHeight="1" s="20">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B15" s="32" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>Percents 2: Actual % change</t>
         </is>
       </c>
-      <c r="C15" s="32" t="n">
+      <c r="C15" s="17" t="n">
         <v>239400</v>
       </c>
-      <c r="D15" s="32" t="n">
+      <c r="D15" s="17" t="n">
         <v>268200</v>
       </c>
-      <c r="E15" s="18" t="inlineStr"/>
-      <c r="F15" s="11">
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="6">
         <f>IF(E15="","",IF(ABS(E15-((D15-C15)/C15))&lt;0.0002,"Correct","Try again"))</f>
         <v/>
       </c>
-      <c r="G15" s="13" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>'=(new - old) / old</t>
         </is>
       </c>
-      <c r="H15" s="32" t="inlineStr">
+      <c r="H15" s="17" t="inlineStr">
         <is>
           <t>Percent change</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="30" t="inlineStr">
+    <row r="16" ht="40" customHeight="1" s="20">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B16" s="30" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>Percents 3: Did actual beat the 12% target?</t>
         </is>
       </c>
-      <c r="C16" s="30" t="inlineStr"/>
-      <c r="D16" s="30" t="inlineStr"/>
-      <c r="E16" s="10" t="inlineStr"/>
-      <c r="F16" s="11">
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="6">
         <f>IF(E16="","",IF(OR(LOWER(E16)="yes",LOWER(E16)="y"),"Correct","Check target vs actual"))</f>
         <v/>
       </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>Answer yes/no after comparing</t>
         </is>
       </c>
-      <c r="H16" s="30" t="inlineStr">
+      <c r="H16" s="15" t="inlineStr">
         <is>
           <t>Interpret</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="35" t="inlineStr">
+    <row r="17"/>
+    <row r="18" ht="16" customHeight="1" s="20">
+      <c r="A18" s="29" t="inlineStr">
         <is>
           <t>Prompt for Students</t>
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
-      <c r="A20" s="36" t="inlineStr">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>When the slide says You Try It, complete only the matching slide-number block. Use formulas where the prompt asks for a calculation; short yes/no interpretation checks can be typed as words.</t>
         </is>
       </c>
-    </row>
-    <row r="21"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="36" t="n"/>
+      <c r="G20" s="36" t="n"/>
+      <c r="H20" s="37" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="38" t="n"/>
+      <c r="B21" s="39" t="n"/>
+      <c r="C21" s="39" t="n"/>
+      <c r="D21" s="39" t="n"/>
+      <c r="E21" s="39" t="n"/>
+      <c r="F21" s="39" t="n"/>
+      <c r="G21" s="39" t="n"/>
+      <c r="H21" s="40" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A18:H18"/>
@@ -1308,10 +1390,10 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="F6:F16">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule type="expression" priority="1" dxfId="1">
       <formula>ISNUMBER(SEARCH("Correct",F6))</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="2" dxfId="0">
       <formula>OR(ISNUMBER(SEARCH("Try",F6)),ISNUMBER(SEARCH("Check",F6)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1331,662 +1413,666 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" style="20" min="1" max="1"/>
+    <col width="42" customWidth="1" style="20" min="2" max="2"/>
+    <col width="18" customWidth="1" style="20" min="3" max="5"/>
+    <col width="24" customWidth="1" style="20" min="6" max="6"/>
+    <col width="28" customWidth="1" style="20" min="7" max="7"/>
+    <col width="16" customWidth="1" style="20" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Next Class Challenge · Connect the Formulas</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Use the same Meridian numbers to build a small model together next class.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="20">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Class Challenge · Connect the Formulas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1" s="20">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>Use the same Meridian numbers to build a small model together in class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1" s="20">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Challenge 1 — Three-Quarter Revenue Model</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="6"/>
+    <row r="7" ht="28" customHeight="1" s="20">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Input A</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Input B</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Formula / Answer</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Coach Check</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Interpretation Prompt</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Skill</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="8" ht="42" customHeight="1" s="20">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Q1-end accounts from 48 start, +12, -3</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>48</v>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>+12 / -3</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr"/>
-      <c r="F8" s="11">
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="6">
         <f>IF(E8="","",IF(ABS(E8-57)&lt;0.0001,"Correct","Try again"))</f>
         <v/>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>What changed from the starting count?</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="25" t="inlineStr">
         <is>
           <t>Arithmetic</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="9" ht="42" customHeight="1" s="20">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>Q2-end accounts after +7, -2 from Q1-end</t>
         </is>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="22">
         <f>E8</f>
         <v/>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>+7 / -2</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr"/>
-      <c r="F9" s="11">
+      <c r="E9" s="11" t="n"/>
+      <c r="F9" s="6">
         <f>IF(E9="","",IF(ABS(E9-(E8+7-2))&lt;0.0001,"Correct","Try again"))</f>
         <v/>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>How does a model reuse prior-period outputs?</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="22" t="inlineStr">
         <is>
           <t>Linked formula</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="10" ht="42" customHeight="1" s="20">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Q3-end accounts after +5, -1 from Q2-end</t>
         </is>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="25">
         <f>E9</f>
         <v/>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>+5 / -1</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr"/>
-      <c r="F10" s="11">
+      <c r="E10" s="11" t="n"/>
+      <c r="F10" s="6">
         <f>IF(E10="","",IF(ABS(E10-(E9+5-1))&lt;0.0001,"Correct","Try again"))</f>
         <v/>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t>Why is linking safer than retyping?</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="25" t="inlineStr">
         <is>
           <t>Linked formula</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11" ht="42" customHeight="1" s="20">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>Q1 fee revenue at $4,200/account</t>
         </is>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="22">
         <f>E8</f>
         <v/>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="22" t="n">
         <v>4200</v>
       </c>
-      <c r="E11" s="20" t="inlineStr"/>
-      <c r="F11" s="11">
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="6">
         <f>IF(E11="","",IF(ABS(E11-(E8*D11))&lt;0.01,"Correct","Try again"))</f>
         <v/>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>What unit is the fee rate using?</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="22" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="12" ht="42" customHeight="1" s="20">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Q2 fee revenue at $4,200/account</t>
         </is>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="25">
         <f>E9</f>
         <v/>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="25" t="n">
         <v>4200</v>
       </c>
-      <c r="E12" s="20" t="inlineStr"/>
-      <c r="F12" s="11">
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="6">
         <f>IF(E12="","",IF(ABS(E12-(E9*D12))&lt;0.01,"Correct","Try again"))</f>
         <v/>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t>What would break if the fee were annual?</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="25" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13" ht="42" customHeight="1" s="20">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>Q3 fee revenue at $4,200/account</t>
         </is>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="22">
         <f>E10</f>
         <v/>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="22" t="n">
         <v>4200</v>
       </c>
-      <c r="E13" s="20" t="inlineStr"/>
-      <c r="F13" s="11">
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="6">
         <f>IF(E13="","",IF(ABS(E13-(E10*D13))&lt;0.01,"Correct","Try again"))</f>
         <v/>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>What trend do you see?</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="14" ht="42" customHeight="1" s="20">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>Cumulative three-quarter fee revenue</t>
         </is>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="25">
         <f>SUM(E11:E13)</f>
         <v/>
       </c>
-      <c r="D14" s="7" t="inlineStr"/>
-      <c r="E14" s="20" t="inlineStr"/>
-      <c r="F14" s="11">
+      <c r="D14" s="25" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="6">
         <f>IF(E14="","",IF(ABS(E14-SUM(E11:E13))&lt;0.01,"Correct","Try again"))</f>
         <v/>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="25" t="inlineStr">
         <is>
           <t>Why use SUM instead of adding manually?</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="25" t="inlineStr">
         <is>
           <t>SUM</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="15" ht="42" customHeight="1" s="20">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>Percent change from Q1 fees to Q3 fees</t>
         </is>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="22">
         <f>E11</f>
         <v/>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="22">
         <f>E13</f>
         <v/>
       </c>
-      <c r="E15" s="21" t="inlineStr"/>
-      <c r="F15" s="11">
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="6">
         <f>IF(E15="","",IF(ABS(E15-((E13-E11)/E11))&lt;0.0002,"Correct","Try again"))</f>
         <v/>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>Which number is the base?</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>Percent change</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18" ht="24" customHeight="1" s="20">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>Challenge 2 — Service-Line Mix</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="19"/>
+    <row r="20" ht="28" customHeight="1" s="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Input A</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Input B</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Formula / Answer</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Coach Check</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Interpretation Prompt</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Skill</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="21" ht="42" customHeight="1" s="20">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>Total Meridian clients</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C21" s="22" t="n">
         <v>57</v>
       </c>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="20" t="inlineStr"/>
-      <c r="F21" s="11">
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="6">
         <f>IF(E21="","",IF(ABS(E21-57)&lt;0.0001,"Correct","Try again"))</f>
         <v/>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>Use this total for the first mix checks.</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="22" ht="42" customHeight="1" s="20">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>Tax clients as % of total</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>22</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="25">
         <f>E21</f>
         <v/>
       </c>
-      <c r="E22" s="21" t="inlineStr"/>
-      <c r="F22" s="11">
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="6">
         <f>IF(E22="","",IF(ABS(E22-(C22/D22))&lt;0.0002,"Correct","Try again"))</f>
         <v/>
       </c>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="G22" s="25" t="inlineStr">
         <is>
           <t>Format as Percentage.</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="25" t="inlineStr">
         <is>
           <t>Ratio as %</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="23" ht="42" customHeight="1" s="20">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>Estate clients as % of total</t>
         </is>
       </c>
-      <c r="C23" s="6" t="n">
+      <c r="C23" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="22">
         <f>E21</f>
         <v/>
       </c>
-      <c r="E23" s="21" t="inlineStr"/>
-      <c r="F23" s="11">
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="6">
         <f>IF(E23="","",IF(ABS(E23-(C23/D23))&lt;0.0002,"Correct","Try again"))</f>
         <v/>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>Is this a change or a share?</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="H23" s="22" t="inlineStr">
         <is>
           <t>Ratio as %</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="42" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="24" ht="42" customHeight="1" s="20">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>Tax + Estate combined % of total</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="25">
         <f>E21</f>
         <v/>
       </c>
-      <c r="E24" s="21" t="inlineStr"/>
-      <c r="F24" s="11">
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="6">
         <f>IF(E24="","",IF(ABS(E24-(C24/D24))&lt;0.0002,"Correct","Try again"))</f>
         <v/>
       </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="G24" s="25" t="inlineStr">
         <is>
           <t>Combine parts before dividing by whole.</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H24" s="25" t="inlineStr">
         <is>
           <t>Ratio as %</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="25" ht="42" customHeight="1" s="20">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>Investment clients after 30% growth</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C25" s="22" t="n">
         <v>17</v>
       </c>
-      <c r="D25" s="15" t="n">
+      <c r="D25" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E25" s="20" t="inlineStr"/>
-      <c r="F25" s="11">
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="6">
         <f>IF(E25="","",IF(ABS(E25-(C25*(1+D25)))&lt;0.01,"Correct","Try again"))</f>
         <v/>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>Should client counts be rounded for a final business recommendation?</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="H25" s="22" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="42" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="26" ht="42" customHeight="1" s="20">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="25" t="inlineStr">
         <is>
           <t>New total clients after investment growth</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="25">
         <f>E25</f>
         <v/>
       </c>
-      <c r="E26" s="20" t="inlineStr"/>
-      <c r="F26" s="11">
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="6">
         <f>IF(E26="","",IF(ABS(E26-(C26+D26))&lt;0.01,"Correct","Try again"))</f>
         <v/>
       </c>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="G26" s="25" t="inlineStr">
         <is>
           <t>Old tax + estate plus new investment count.</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H26" s="25" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="42" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="27" ht="42" customHeight="1" s="20">
+      <c r="A27" s="22" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>New investment % of new total</t>
         </is>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="22">
         <f>E25</f>
         <v/>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="22">
         <f>E26</f>
         <v/>
       </c>
-      <c r="E27" s="21" t="inlineStr"/>
-      <c r="F27" s="11">
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="6">
         <f>IF(E27="","",IF(ABS(E27-(C27/D27))&lt;0.0002,"Correct","Try again"))</f>
         <v/>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G27" s="22" t="inlineStr">
         <is>
           <t>How did the mix change?</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="H27" s="22" t="inlineStr">
         <is>
           <t>Ratio as %</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="42" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="28" ht="42" customHeight="1" s="20">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="25" t="inlineStr">
         <is>
           <t>One-sentence business interpretation</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr"/>
-      <c r="D28" s="7" t="inlineStr"/>
-      <c r="E28" s="20" t="inlineStr"/>
-      <c r="F28" s="11" t="inlineStr"/>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="C28" s="25" t="n"/>
+      <c r="D28" s="25" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="25" t="inlineStr">
         <is>
           <t>Explain what changed in the service-line mix.</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="H28" s="25" t="inlineStr">
         <is>
           <t>Interpret</t>
         </is>
@@ -2000,15 +2086,15 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="F8:F27">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule type="expression" priority="1" dxfId="1">
       <formula>ISNUMBER(SEARCH("Correct",F8))</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="2" dxfId="0">
       <formula>OR(ISNUMBER(SEARCH("Try",F8)),ISNUMBER(SEARCH("Check",F8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="portrait" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -2019,447 +2105,451 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" style="20" min="1" max="1"/>
+    <col width="34" customWidth="1" style="20" min="2" max="2"/>
+    <col width="46" customWidth="1" style="20" min="3" max="3"/>
+    <col width="36" customWidth="1" style="20" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="20">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Formula Reference Card · BUS123 MATH-M01</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="24" customHeight="1" s="20">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Use this as a syntax reminder, then return to the yellow cells.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="3"/>
+    <row r="4" ht="24" customHeight="1" s="20">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>ARITHMETIC OPERATIONS</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="5" ht="28" customHeight="1" s="20">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Excel Syntax</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Use It For</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Watch Out For</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="6" ht="34" customHeight="1" s="20">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Addition range</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>'=SUM(B2:B10)</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>Adds a range</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>Do not type every number if a range exists</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7" ht="34" customHeight="1" s="20">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>Subtraction</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>'=B5-C5</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>Difference between two cells</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>Check units</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="8" ht="34" customHeight="1" s="20">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Multiplication</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>'=B3*C3</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>Quantity times fee/rate</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>Check time period</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="9" ht="34" customHeight="1" s="20">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>Division</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>'=B7/C7</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>Total divided by count</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>Denominator cannot be zero</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="10"/>
+    <row r="11" ht="24" customHeight="1" s="20">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>FRACTIONS &amp; RATIOS</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+    <row r="12" ht="28" customHeight="1" s="20">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Excel Syntax</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Use It For</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Watch Out For</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13" ht="34" customHeight="1" s="20">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>Fraction to decimal</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>'=B2/C2</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>Numerator divided by denominator</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>Denominator is the whole</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="14" ht="34" customHeight="1" s="20">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Fraction as percent</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>'=B2/C2</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t>Same formula, formatted as %</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="25" t="inlineStr">
         <is>
           <t>Do not multiply by 100</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="15" ht="34" customHeight="1" s="20">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>Part of total</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>'=part/whole</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>Share of a total</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>Use current total</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
+    <row r="16"/>
+    <row r="17" ht="24" customHeight="1" s="20">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>PERCENT CALCULATIONS</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="18" ht="28" customHeight="1" s="20">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Excel Syntax</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Use It For</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Watch Out For</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="19" ht="34" customHeight="1" s="20">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>% of a whole</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>'=B4*B5</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>Whole times rate</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>Rate as decimal or percent</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="20" ht="34" customHeight="1" s="20">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>Grow by X%</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>'=B4*(1+B5)</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="25" t="inlineStr">
         <is>
           <t>Base increased by rate</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="25" t="inlineStr">
         <is>
           <t>Use 1 + rate</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="21" ht="34" customHeight="1" s="20">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>% change</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>'=(new-old)/old</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>Change over time</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>Old value is the denominator</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="34" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="22" ht="34" customHeight="1" s="20">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>Ratio as %</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>'=part/whole</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="25" t="inlineStr">
         <is>
           <t>Share at one point in time</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="25" t="inlineStr">
         <is>
           <t>Different from percent change</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
+    <row r="23"/>
+    <row r="24" ht="24" customHeight="1" s="20">
+      <c r="A24" s="34" t="inlineStr">
         <is>
           <t>COMMON MISTAKES</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="25" ht="28" customHeight="1" s="20">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Excel Syntax</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Use It For</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Watch Out For</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="26" ht="34" customHeight="1" s="20">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t>Unit mismatch</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>Label units in headers</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="25" t="inlineStr">
         <is>
           <t>Quarterly vs annual, dollars vs cents</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="25" t="inlineStr">
         <is>
           <t>Excel will not warn you</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="27" ht="34" customHeight="1" s="20">
+      <c r="A27" s="22" t="inlineStr">
         <is>
           <t>Wrong base</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>'=(new-old)/old</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>Base is older number</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>Do not divide by new value</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="28" ht="34" customHeight="1" s="20">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t>Hardcoded values</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>'=B2*B3</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="25" t="inlineStr">
         <is>
           <t>Reference cells so formulas update</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D28" s="25" t="inlineStr">
         <is>
           <t>Avoid =57*4200 when cells exist</t>
         </is>
@@ -2475,6 +2565,6 @@
     <mergeCell ref="A11:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="portrait" fitToHeight="0"/>
 </worksheet>
 </file>
--- a/MATH/M01/bus123-math-m01-l01-starter.xlsx
+++ b/MATH/M01/bus123-math-m01-l01-starter.xlsx
@@ -2,9 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="580" windowWidth="25600" windowHeight="15240" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" state="visible" r:id="rId2"/>
@@ -12,20 +9,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -58,10 +52,8 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <color rgb="FF1A1F2C"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -81,8 +73,20 @@
       <color rgb="FF355773"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFB8843D"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF355773"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -139,15 +143,49 @@
         <fgColor rgb="FFB8843D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0E1116"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF3EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2EEE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0E1116"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF3EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2EEE5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="12">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FFE5E1D6"/>
@@ -161,7 +199,6 @@
       <bottom style="thin">
         <color rgb="FFE5E1D6"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -176,21 +213,16 @@
       <bottom style="thin">
         <color rgb="FFE5E1D6"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color rgb="FFE5E1D6"/>
       </top>
       <bottom style="thin">
         <color rgb="FFE5E1D6"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
       <right style="thin">
         <color rgb="FFE5E1D6"/>
       </right>
@@ -200,82 +232,56 @@
       <bottom style="thin">
         <color rgb="FFE5E1D6"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color rgb="FFE5E1D6"/>
       </top>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
-      <left/>
       <right style="thin">
         <color rgb="FFE5E1D6"/>
       </right>
       <top style="thin">
         <color rgb="FFE5E1D6"/>
       </top>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color rgb="FF4A7C5E"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
-      <left/>
       <right style="thin">
         <color rgb="FFE5E1D6"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color rgb="FF4A7C5E"/>
       </left>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color rgb="FFE5E1D6"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color rgb="FFE5E1D6"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
       <right style="thin">
         <color rgb="FFE5E1D6"/>
       </right>
-      <top/>
       <bottom style="thin">
         <color rgb="FFE5E1D6"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -379,41 +385,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
+        <patternFill>
+          <bgColor rgb="FFD9EAD3"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
+        <patternFill>
+          <bgColor rgb="FFD9EAD3"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -486,7 +532,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -528,72 +574,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -649,7 +637,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -658,13 +646,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -698,17 +686,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -763,8 +740,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -772,7 +747,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
@@ -794,8 +769,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="20">
       <c r="A5" s="26" t="inlineStr">
         <is>
@@ -803,7 +776,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7" ht="24" customHeight="1" s="20">
       <c r="A7" s="1" t="inlineStr">
         <is>
@@ -864,8 +836,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
     <row r="14" ht="24" customHeight="1" s="20">
       <c r="A14" s="26" t="inlineStr">
         <is>
@@ -873,7 +843,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16" ht="28" customHeight="1" s="20">
       <c r="A16" s="2" t="inlineStr">
         <is>
@@ -946,8 +915,6 @@
       <c r="G19" s="23" t="n"/>
       <c r="H19" s="24" t="n"/>
     </row>
-    <row r="20"/>
-    <row r="21"/>
     <row r="22" ht="24" customHeight="1" s="20">
       <c r="A22" s="27" t="inlineStr">
         <is>
@@ -955,7 +922,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="28" t="inlineStr">
         <is>
@@ -981,8 +947,7 @@
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="A24:H25"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToHeight="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1017,8 +982,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5" ht="32" customHeight="1" s="20">
       <c r="A5" s="2" t="inlineStr">
         <is>
@@ -1349,7 +1312,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18" ht="16" customHeight="1" s="20">
       <c r="A18" s="29" t="inlineStr">
         <is>
@@ -1357,7 +1319,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="31" t="inlineStr">
         <is>
@@ -1402,7 +1363,7 @@
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1410,7 +1371,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
@@ -1437,8 +1398,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="20">
       <c r="A5" s="26" t="inlineStr">
         <is>
@@ -1446,7 +1405,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7" ht="28" customHeight="1" s="20">
       <c r="A7" s="2" t="inlineStr">
         <is>
@@ -1765,8 +1723,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17"/>
     <row r="18" ht="24" customHeight="1" s="20">
       <c r="A18" s="27" t="inlineStr">
         <is>
@@ -1774,7 +1730,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20" ht="28" customHeight="1" s="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
@@ -2093,8 +2048,7 @@
       <formula>OR(ISNUMBER(SEARCH("Try",F8)),ISNUMBER(SEARCH("Check",F8)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToHeight="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2102,469 +2056,169 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="20" min="1" max="1"/>
-    <col width="34" customWidth="1" style="20" min="2" max="2"/>
-    <col width="46" customWidth="1" style="20" min="3" max="3"/>
-    <col width="36" customWidth="1" style="20" min="4" max="4"/>
+    <col width="21.11000061035156" customWidth="1" style="20" min="1" max="1"/>
+    <col width="25.55999946594238" customWidth="1" style="20" min="2" max="2"/>
+    <col width="34.43999862670898" customWidth="1" style="20" min="3" max="3"/>
+    <col width="33.33000183105469" customWidth="1" style="20" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="20">
-      <c r="A1" s="19" t="inlineStr">
-        <is>
-          <t>Formula Reference Card · BUS123 MATH-M01</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1" s="20">
-      <c r="A2" s="26" t="inlineStr">
-        <is>
-          <t>Use this as a syntax reminder, then return to the yellow cells.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4" ht="24" customHeight="1" s="20">
-      <c r="A4" s="26" t="inlineStr">
-        <is>
-          <t>ARITHMETIC OPERATIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" s="20">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="1" ht="31.5" customHeight="1" s="20">
+      <c r="A1" s="54" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Excel Syntax</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Use It For</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="B1" s="54" t="inlineStr">
+        <is>
+          <t>Excel Pattern</t>
+        </is>
+      </c>
+      <c r="C1" s="54" t="inlineStr">
+        <is>
+          <t>Plain-English Meaning</t>
+        </is>
+      </c>
+      <c r="D1" s="54" t="inlineStr">
         <is>
           <t>Watch Out For</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1" s="20">
-      <c r="A6" s="25" t="inlineStr">
+    <row r="2" ht="31.5" customHeight="1" s="20">
+      <c r="A2" s="58" t="inlineStr">
         <is>
           <t>Addition range</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>'=SUM(B2:B10)</t>
-        </is>
-      </c>
-      <c r="C6" s="25" t="inlineStr">
-        <is>
-          <t>Adds a range</t>
-        </is>
-      </c>
-      <c r="D6" s="25" t="inlineStr">
-        <is>
-          <t>Do not type every number if a range exists</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1" s="20">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="B2" s="60" t="inlineStr">
+        <is>
+          <t>=SUM(B2:B10)</t>
+        </is>
+      </c>
+      <c r="C2" s="58" t="inlineStr">
+        <is>
+          <t>Adds a column or row of related numbers.</t>
+        </is>
+      </c>
+      <c r="D2" s="61" t="inlineStr">
+        <is>
+          <t>Do not type every number if a range exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="31.5" customHeight="1" s="20">
+      <c r="A3" s="58" t="inlineStr">
         <is>
           <t>Subtraction</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>'=B5-C5</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>Difference between two cells</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>Check units</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1" s="20">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
+        <is>
+          <t>=B5-C5</t>
+        </is>
+      </c>
+      <c r="C3" s="58" t="inlineStr">
+        <is>
+          <t>Finds the difference between two cells.</t>
+        </is>
+      </c>
+      <c r="D3" s="61" t="inlineStr">
+        <is>
+          <t>Check that both cells use the same units.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="31.5" customHeight="1" s="20">
+      <c r="A4" s="58" t="inlineStr">
         <is>
           <t>Multiplication</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>'=B3*C3</t>
-        </is>
-      </c>
-      <c r="C8" s="25" t="inlineStr">
-        <is>
-          <t>Quantity times fee/rate</t>
-        </is>
-      </c>
-      <c r="D8" s="25" t="inlineStr">
-        <is>
-          <t>Check time period</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="34" customHeight="1" s="20">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="B4" s="60" t="inlineStr">
+        <is>
+          <t>=B3*C3</t>
+        </is>
+      </c>
+      <c r="C4" s="58" t="inlineStr">
+        <is>
+          <t>Multiplies quantity by fee, rate, or price.</t>
+        </is>
+      </c>
+      <c r="D4" s="61" t="inlineStr">
+        <is>
+          <t>Check the time period before multiplying.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31.5" customHeight="1" s="20">
+      <c r="A5" s="58" t="inlineStr">
         <is>
           <t>Division</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>'=B7/C7</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
-        <is>
-          <t>Total divided by count</t>
-        </is>
-      </c>
-      <c r="D9" s="22" t="inlineStr">
-        <is>
-          <t>Denominator cannot be zero</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11" ht="24" customHeight="1" s="20">
-      <c r="A11" s="27" t="inlineStr">
-        <is>
-          <t>FRACTIONS &amp; RATIOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" s="20">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Concept</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Excel Syntax</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Use It For</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Watch Out For</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1" s="20">
-      <c r="A13" s="22" t="inlineStr">
-        <is>
-          <t>Fraction to decimal</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>'=B2/C2</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
-        <is>
-          <t>Numerator divided by denominator</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
-        <is>
-          <t>Denominator is the whole</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="34" customHeight="1" s="20">
-      <c r="A14" s="25" t="inlineStr">
-        <is>
-          <t>Fraction as percent</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>'=B2/C2</t>
-        </is>
-      </c>
-      <c r="C14" s="25" t="inlineStr">
-        <is>
-          <t>Same formula, formatted as %</t>
-        </is>
-      </c>
-      <c r="D14" s="25" t="inlineStr">
-        <is>
-          <t>Do not multiply by 100</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="34" customHeight="1" s="20">
-      <c r="A15" s="22" t="inlineStr">
-        <is>
-          <t>Part of total</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>'=part/whole</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>Share of a total</t>
-        </is>
-      </c>
-      <c r="D15" s="22" t="inlineStr">
-        <is>
-          <t>Use current total</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17" ht="24" customHeight="1" s="20">
-      <c r="A17" s="33" t="inlineStr">
-        <is>
-          <t>PERCENT CALCULATIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1" s="20">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Concept</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Excel Syntax</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Use It For</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Watch Out For</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="34" customHeight="1" s="20">
-      <c r="A19" s="22" t="inlineStr">
-        <is>
-          <t>% of a whole</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t>'=B4*B5</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>Whole times rate</t>
-        </is>
-      </c>
-      <c r="D19" s="22" t="inlineStr">
-        <is>
-          <t>Rate as decimal or percent</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="34" customHeight="1" s="20">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>Grow by X%</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>'=B4*(1+B5)</t>
-        </is>
-      </c>
-      <c r="C20" s="25" t="inlineStr">
-        <is>
-          <t>Base increased by rate</t>
-        </is>
-      </c>
-      <c r="D20" s="25" t="inlineStr">
-        <is>
-          <t>Use 1 + rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="34" customHeight="1" s="20">
-      <c r="A21" s="22" t="inlineStr">
-        <is>
-          <t>% change</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>'=(new-old)/old</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="inlineStr">
-        <is>
-          <t>Change over time</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="inlineStr">
-        <is>
-          <t>Old value is the denominator</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="34" customHeight="1" s="20">
-      <c r="A22" s="25" t="inlineStr">
-        <is>
-          <t>Ratio as %</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>'=part/whole</t>
-        </is>
-      </c>
-      <c r="C22" s="25" t="inlineStr">
-        <is>
-          <t>Share at one point in time</t>
-        </is>
-      </c>
-      <c r="D22" s="25" t="inlineStr">
-        <is>
-          <t>Different from percent change</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24" ht="24" customHeight="1" s="20">
-      <c r="A24" s="34" t="inlineStr">
-        <is>
-          <t>COMMON MISTAKES</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1" s="20">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Concept</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Excel Syntax</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Use It For</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Watch Out For</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="34" customHeight="1" s="20">
-      <c r="A26" s="25" t="inlineStr">
-        <is>
-          <t>Unit mismatch</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>Label units in headers</t>
-        </is>
-      </c>
-      <c r="C26" s="25" t="inlineStr">
-        <is>
-          <t>Quarterly vs annual, dollars vs cents</t>
-        </is>
-      </c>
-      <c r="D26" s="25" t="inlineStr">
-        <is>
-          <t>Excel will not warn you</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="34" customHeight="1" s="20">
-      <c r="A27" s="22" t="inlineStr">
-        <is>
-          <t>Wrong base</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>'=(new-old)/old</t>
-        </is>
-      </c>
-      <c r="C27" s="22" t="inlineStr">
-        <is>
-          <t>Base is older number</t>
-        </is>
-      </c>
-      <c r="D27" s="22" t="inlineStr">
-        <is>
-          <t>Do not divide by new value</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="34" customHeight="1" s="20">
-      <c r="A28" s="25" t="inlineStr">
-        <is>
-          <t>Hardcoded values</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>'=B2*B3</t>
-        </is>
-      </c>
-      <c r="C28" s="25" t="inlineStr">
-        <is>
-          <t>Reference cells so formulas update</t>
-        </is>
-      </c>
-      <c r="D28" s="25" t="inlineStr">
-        <is>
-          <t>Avoid =57*4200 when cells exist</t>
-        </is>
-      </c>
-    </row>
+      <c r="B5" s="60" t="inlineStr">
+        <is>
+          <t>=B7/C7</t>
+        </is>
+      </c>
+      <c r="C5" s="58" t="inlineStr">
+        <is>
+          <t>Splits a total across a count or base.</t>
+        </is>
+      </c>
+      <c r="D5" s="61" t="inlineStr">
+        <is>
+          <t>The denominator cannot be zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="31.5" customHeight="1" s="20">
+      <c r="A6" s="58" t="inlineStr">
+        <is>
+          <t>Percent share</t>
+        </is>
+      </c>
+      <c r="B6" s="60" t="inlineStr">
+        <is>
+          <t>=B2/C2</t>
+        </is>
+      </c>
+      <c r="C6" s="58" t="inlineStr">
+        <is>
+          <t>Shows a part as a share of the whole.</t>
+        </is>
+      </c>
+      <c r="D6" s="61" t="inlineStr">
+        <is>
+          <t>Format as percent instead of multiplying by 100.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1" s="20"/>
+    <row r="8" ht="34" customHeight="1" s="20"/>
+    <row r="9" ht="34" customHeight="1" s="20"/>
+    <row r="11" ht="24" customHeight="1" s="20"/>
+    <row r="12" ht="28" customHeight="1" s="20"/>
+    <row r="13" ht="34" customHeight="1" s="20"/>
+    <row r="14" ht="34" customHeight="1" s="20"/>
+    <row r="15" ht="34" customHeight="1" s="20"/>
+    <row r="17" ht="24" customHeight="1" s="20"/>
+    <row r="18" ht="28" customHeight="1" s="20"/>
+    <row r="19" ht="34" customHeight="1" s="20"/>
+    <row r="20" ht="34" customHeight="1" s="20"/>
+    <row r="21" ht="34" customHeight="1" s="20"/>
+    <row r="22" ht="34" customHeight="1" s="20"/>
+    <row r="24" ht="24" customHeight="1" s="20"/>
+    <row r="25" ht="28" customHeight="1" s="20"/>
+    <row r="26" ht="34" customHeight="1" s="20"/>
+    <row r="27" ht="34" customHeight="1" s="20"/>
+    <row r="28" ht="34" customHeight="1" s="20"/>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToHeight="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>